--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513303_ELIMINGRD12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513303_ELIMINGRD12FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0979</v>
+        <v>5.6378</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9346</v>
+        <v>4.9247</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1632</v>
+        <v>0.7131</v>
       </c>
       <c r="G2" t="n">
-        <v>1.923</v>
+        <v>2.0421</v>
       </c>
       <c r="H2" t="n">
-        <v>1.605</v>
+        <v>1.7423</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3181</v>
+        <v>0.2998</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4102</v>
+        <v>3.663</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0485</v>
+        <v>2.2606</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3617</v>
+        <v>1.4023</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4871</v>
+        <v>-1.6209</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4435</v>
+        <v>-0.5184</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0437</v>
+        <v>-1.1026</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5744</v>
+        <v>0.0378</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3247</v>
+        <v>0.0406</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2497</v>
+        <v>-0.0028</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6009</v>
+        <v>4.1455</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4476</v>
+        <v>3.4117</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1533</v>
+        <v>0.7338</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6157</v>
+        <v>1.6195</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2798</v>
+        <v>3.3103</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6641</v>
+        <v>-1.6908</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5029</v>
+        <v>2.6299</v>
       </c>
       <c r="K3" t="n">
-        <v>3.659</v>
+        <v>3.7563</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.156</v>
+        <v>-1.1264</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8873</v>
+        <v>-1.0104</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3791</v>
+        <v>-0.446</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5081</v>
+        <v>-0.5644</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3047</v>
+        <v>0.8902</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7451</v>
+        <v>0.5344</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5596</v>
+        <v>0.3558</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2329</v>
+        <v>3.5406</v>
       </c>
       <c r="E4" t="n">
-        <v>6.052</v>
+        <v>3.38</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8192</v>
+        <v>0.1606</v>
       </c>
       <c r="G4" t="n">
-        <v>2.349</v>
+        <v>1.8565</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4447</v>
+        <v>2.6587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9043</v>
+        <v>-0.8022</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8429</v>
+        <v>3.3024</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8813</v>
+        <v>2.5967</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9616</v>
+        <v>0.7057</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4939</v>
+        <v>-1.4459</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4366</v>
+        <v>0.062</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0574</v>
+        <v>-1.5078</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0003</v>
+        <v>2.1421</v>
       </c>
       <c r="S4" t="n">
-        <v>0.944</v>
+        <v>0.5478</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0097</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0657</v>
+        <v>-0.2561</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.398</v>
+        <v>3.4603</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9004</v>
+        <v>5.2108</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4976</v>
+        <v>-1.7505</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7476</v>
+        <v>2.3535</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5836</v>
+        <v>1.4327</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8361</v>
+        <v>0.9208</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0141</v>
+        <v>3.9731</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4065</v>
+        <v>1.9629</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6075</v>
+        <v>2.0102</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2665</v>
+        <v>-1.6196</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1771</v>
+        <v>-0.5302</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4436</v>
+        <v>-1.0895</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2006</v>
+        <v>0.9737</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5104</v>
+        <v>0.1652</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6871</v>
+        <v>0.9903</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1767</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7695</v>
+        <v>1.742</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3578</v>
+        <v>1.5445</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5883</v>
+        <v>0.1975</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0101</v>
+        <v>0.1931</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0953</v>
+        <v>1.7051</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9148</v>
+        <v>-1.512</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6466</v>
+        <v>1.4259</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6813</v>
+        <v>2.1142</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9653</v>
+        <v>-0.6883</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6365</v>
+        <v>-1.2328</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.586</v>
+        <v>-0.4091</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0505</v>
+        <v>-0.8236</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2006</v>
+        <v>1.1684</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5221</v>
+        <v>0.0494</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2889</v>
+        <v>0.4818</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2332</v>
+        <v>-0.4324</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.9191</v>
+        <v>0.3311</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.9191</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2456</v>
+        <v>1.7184</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1983</v>
+        <v>4.4672</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0473</v>
+        <v>-2.7488</v>
       </c>
       <c r="G7" t="n">
-        <v>0.315</v>
+        <v>3.0944</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3112</v>
+        <v>1.1182</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0038</v>
+        <v>1.9763</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1312</v>
+        <v>4.8299</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3945</v>
+        <v>1.7576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5256</v>
+        <v>3.0723</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1838</v>
+        <v>-1.7354</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7057</v>
+        <v>-0.6394</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5218</v>
+        <v>-1.096</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8002</v>
+        <v>2.1421</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8002</v>
+        <v>2.1421</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5102</v>
+        <v>-0.5171</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0671</v>
+        <v>-0.3627</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.1544</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3798</v>
+        <v>-3.0011</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3798</v>
+        <v>-3.0011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0193</v>
+        <v>1.6903</v>
       </c>
       <c r="E8" t="n">
-        <v>0.522</v>
+        <v>1.6233</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4972</v>
+        <v>0.067</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1888</v>
+        <v>-1.5602</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7654</v>
+        <v>-0.4255</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5765</v>
+        <v>-1.1347</v>
       </c>
       <c r="J8" t="n">
-        <v>1.269</v>
+        <v>-1.9407</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0594</v>
+        <v>-0.6927</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7904</v>
+        <v>-1.248</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0802</v>
+        <v>0.3804</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2941</v>
+        <v>0.2672</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7862</v>
+        <v>0.1132</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2003</v>
+        <v>0.3895</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2006</v>
+        <v>0.3895</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.71</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3466</v>
+        <v>0.5113</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3634</v>
+        <v>-0.5808</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3401</v>
+        <v>2.9305</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5999</v>
+        <v>3.0526</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2598</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="9">
@@ -1111,31 +1111,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.335</v>
+        <v>0.5584</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4138</v>
+        <v>0.8196</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0788</v>
+        <v>-0.2611</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.479</v>
+        <v>0.3557</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3592</v>
+        <v>0.3069</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1198</v>
+        <v>0.0489</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0122</v>
+        <v>0.2898</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7362</v>
+        <v>-0.3104</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.276</v>
+        <v>0.6002</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5332</v>
+        <v>0.0659</v>
       </c>
       <c r="N10" t="n">
-        <v>0.377</v>
+        <v>0.6172</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1562</v>
+        <v>-0.5513</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4656</v>
+        <v>-0.1747</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5734</v>
+        <v>0.5298</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8922</v>
+        <v>-0.7044</v>
       </c>
       <c r="V10" t="n">
-        <v>2.8795</v>
+        <v>-0.4016</v>
       </c>
       <c r="W10" t="n">
-        <v>2.9994</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.12</v>
+        <v>-0.4016</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1332</v>
+        <v>-1.689</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4147</v>
+        <v>-1.9323</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2816</v>
+        <v>0.2434</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.593</v>
+        <v>-0.6234</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2222</v>
+        <v>-1.2295</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6292</v>
+        <v>0.6061</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8343</v>
+        <v>-0.763</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9143</v>
+        <v>-0.844</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2414</v>
+        <v>0.1396</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3079</v>
+        <v>-0.3855</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2202</v>
+        <v>-0.7487</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.1957</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.64</v>
+        <v>-0.5531</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0874</v>
+        <v>-3.2929</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9694</v>
+        <v>-2.9813</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1179</v>
+        <v>-0.3116</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.0849</v>
+        <v>-4.0677</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2783</v>
+        <v>-2.2506</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8066</v>
+        <v>-1.8171</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.8826</v>
+        <v>-3.7048</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.7266</v>
+        <v>-2.5784</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.156</v>
+        <v>-1.1264</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2023</v>
+        <v>-0.363</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4483</v>
+        <v>0.3278</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6506</v>
+        <v>-0.6907</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9425</v>
+        <v>-0.1615</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3466</v>
+        <v>0.4439</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5959</v>
+        <v>-0.6055</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1398</v>
+        <v>0.1574</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4586</v>
+        <v>-5.1696</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7062</v>
+        <v>-2.195</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7524</v>
+        <v>-2.9746</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2844</v>
+        <v>-0.2913</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1848</v>
+        <v>1.1658</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4691</v>
+        <v>-1.4572</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2544</v>
+        <v>-0.1756</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0997</v>
+        <v>1.129</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3541</v>
+        <v>-1.3046</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0299</v>
+        <v>-0.1157</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0851</v>
+        <v>0.0369</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.115</v>
+        <v>-0.1526</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5944</v>
+        <v>-0.282</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4512</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1432</v>
+        <v>-0.21</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.7793</v>
+        <v>-2.8437</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7793</v>
+        <v>-2.8437</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.91970000000001</v>
+        <v>13.2576</v>
       </c>
       <c r="E14" t="n">
-        <v>16.636</v>
+        <v>19.189</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7164</v>
+        <v>-5.9312</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6077</v>
+        <v>5.888</v>
       </c>
       <c r="H14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.842300000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.1021</v>
+        <v>-3.9542</v>
       </c>
       <c r="J14" t="n">
-        <v>12.7332</v>
+        <v>14.4457</v>
       </c>
       <c r="K14" t="n">
-        <v>10.364</v>
+        <v>11.4597</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3691</v>
+        <v>2.986000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.1253</v>
+        <v>-8.5578</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6540000000000001</v>
+        <v>-1.6175</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.4714</v>
+        <v>-6.940299999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>7.001899999999999</v>
+        <v>6.815700000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.0024</v>
+        <v>-7.7896</v>
       </c>
       <c r="R14" t="n">
-        <v>15.0042</v>
+        <v>14.6051</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6111000000000001</v>
+        <v>-0.2630999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2469</v>
+        <v>3.7056</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.858</v>
+        <v>-3.9688</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9212000000000002</v>
+        <v>0.8168999999999991</v>
       </c>
       <c r="W14" t="n">
-        <v>8.658300000000001</v>
+        <v>8.827</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.7372</v>
+        <v>-8.010200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8597</v>
+        <v>3.8422</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5069</v>
+        <v>5.4323</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6472</v>
+        <v>-1.5902</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1386</v>
+        <v>5.0909</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6875</v>
+        <v>0.6301</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4512</v>
+        <v>4.4609</v>
       </c>
       <c r="J15" t="n">
-        <v>7.228</v>
+        <v>7.4854</v>
       </c>
       <c r="K15" t="n">
-        <v>2.303</v>
+        <v>2.4273</v>
       </c>
       <c r="L15" t="n">
-        <v>4.925</v>
+        <v>5.0581</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0893</v>
+        <v>-2.3944</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6155</v>
+        <v>-1.7972</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4738</v>
+        <v>-0.5972</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7425</v>
+        <v>0.6391</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5007</v>
+        <v>1.0032</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7582</v>
+        <v>-0.3641</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7794</v>
+        <v>0.8384</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7794</v>
+        <v>0.8384</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5999</v>
+        <v>0.8093</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5999</v>
+        <v>1.1241</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.3148</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5999</v>
+        <v>0.0343</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-1.3871</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5999</v>
+        <v>1.4214</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5999</v>
+        <v>0.2104</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-1.1109</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5999</v>
+        <v>1.3213</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.1761</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.2762</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.1908</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.9137</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.7229</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4424</v>
+        <v>0.6079</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1169</v>
+        <v>0.6079</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1189</v>
+        <v>0.6079</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3327</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4516</v>
+        <v>0.6079</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1075</v>
+        <v>0.6079</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1742</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2817</v>
+        <v>0.6079</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0114</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1585</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1699</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6002</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6002</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2767</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0094</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2861</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0214</v>
+        <v>0.0097</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1328</v>
+        <v>0.8439</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1543</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0599</v>
+        <v>-1.5745</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6442</v>
+        <v>-2.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5843</v>
+        <v>0.5268</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2617</v>
+        <v>-0.2456</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02</v>
+        <v>-0.9185</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2417</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3216</v>
+        <v>-1.3289</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6642</v>
+        <v>-1.1829</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6574</v>
+        <v>-0.146</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0384</v>
+        <v>0.3369</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1289</v>
+        <v>0.2317</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1673</v>
+        <v>0.1052</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.8316</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8316</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.0648</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3051</v>
+        <v>1.1776</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9598</v>
+        <v>-1.2424</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5577</v>
+        <v>-0.0711</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0776</v>
+        <v>-0.6676</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5199</v>
+        <v>0.5966</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3143</v>
+        <v>1.3013</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9560999999999999</v>
+        <v>0.0205</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6418</v>
+        <v>1.2808</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2434</v>
+        <v>-1.3723</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1215</v>
+        <v>-0.6882</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1219</v>
+        <v>-0.6842</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6002</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4001</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2965</v>
+        <v>0.0062</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.18</v>
+        <v>-0.1237</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1165</v>
+        <v>0.1299</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8527</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0534</v>
+        <v>-0.0434</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7993</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9104</v>
+        <v>-0.9644</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6442</v>
+        <v>-0.6676</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2662</v>
+        <v>-0.2968</v>
       </c>
       <c r="J20" t="n">
-        <v>0.14</v>
+        <v>0.1421</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0504</v>
+        <v>-1.1065</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6642</v>
+        <v>-0.6882</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3862</v>
+        <v>-0.4184</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0578</v>
+        <v>0.0526</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1934</v>
+        <v>-0.1855</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2511</v>
+        <v>0.2381</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4521</v>
+        <v>-1.4688</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7244</v>
+        <v>-0.527</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2722</v>
+        <v>-0.9418</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3536</v>
+        <v>-1.4384</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0473</v>
+        <v>-1.1839</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3062</v>
+        <v>-0.2545</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.1681</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5612</v>
+        <v>0.1437</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6323</v>
+        <v>0.0244</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2825</v>
+        <v>-1.6065</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6086</v>
+        <v>-1.3276</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3261</v>
+        <v>-0.2789</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.6013</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-6.0017</v>
+        <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4004</v>
+        <v>0.9737</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8434</v>
+        <v>-0.3099</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4293</v>
+        <v>-0.0009</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4142</v>
+        <v>-0.309</v>
       </c>
       <c r="V21" t="n">
-        <v>2.6593</v>
+        <v>0.2795</v>
       </c>
       <c r="W21" t="n">
-        <v>2.9191</v>
+        <v>0.2795</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.758</v>
+        <v>-1.4881</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9142</v>
+        <v>-0.7542</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8438</v>
+        <v>-0.7338</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3658</v>
+        <v>-0.1652</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1102</v>
+        <v>0.1722</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2556</v>
+        <v>-0.3373</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1419</v>
+        <v>1.4306</v>
       </c>
       <c r="K22" t="n">
-        <v>0.14</v>
+        <v>1.9812</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0019</v>
+        <v>-0.5507</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5077</v>
+        <v>-1.5957</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2502</v>
+        <v>-1.8091</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2575</v>
+        <v>0.2133</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-4.4789</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0003</v>
+        <v>-5.8421</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0003</v>
+        <v>1.3632</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.652</v>
+        <v>0.4345</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3156</v>
+        <v>0.6562</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3364</v>
+        <v>-0.2218</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2598</v>
+        <v>2.7216</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2598</v>
+        <v>3.0011</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="23">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2849</v>
+        <v>-2.0782</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0406</v>
+        <v>0.2109</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2443</v>
+        <v>-2.2892</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1756</v>
+        <v>-0.174</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1756</v>
+        <v>-0.174</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2817</v>
+        <v>0.3208</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2817</v>
+        <v>0.3208</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4573</v>
+        <v>-0.4947</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4573</v>
+        <v>-0.4947</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7097</v>
+        <v>-0.4622</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3223</v>
+        <v>-0.1098</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3875</v>
+        <v>-0.3523</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0098</v>
+        <v>-2.9015</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1365</v>
+        <v>-1.2028</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1462</v>
+        <v>-1.6987</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8175</v>
+        <v>-2.45</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8733</v>
+        <v>-0.9571</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9442</v>
+        <v>-1.4929</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9307</v>
+        <v>-1.8081</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3727</v>
+        <v>-0.4874</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-1.3207</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8869</v>
+        <v>-0.6419</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5006</v>
+        <v>-0.4696</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3862</v>
+        <v>-0.1723</v>
       </c>
       <c r="P24" t="n">
-        <v>1.4004</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4004</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8069</v>
+        <v>-0.3415</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0671</v>
+        <v>0.0785</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2602</v>
+        <v>-0.42</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.3995</v>
+        <v>0.2795</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3995</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1936</v>
+        <v>-3.5818</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6157</v>
+        <v>-0.0324</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5779</v>
+        <v>-3.5494</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3882</v>
+        <v>-2.8466</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9016</v>
+        <v>-1.8853</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4866</v>
+        <v>-0.9613</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.9284</v>
+        <v>-0.7994</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5362</v>
+        <v>-0.2564</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3922</v>
+        <v>-0.5429</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4598</v>
+        <v>-2.0473</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3653</v>
+        <v>-1.6289</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0945</v>
+        <v>-0.4184</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4001</v>
+        <v>1.3632</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6002</v>
+        <v>1.3632</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6651</v>
+        <v>0.3438</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1466</v>
+        <v>0.767</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5185</v>
+        <v>-0.4232</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2598</v>
+        <v>-2.4421</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.1998</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.5945</v>
+        <v>-5.0581</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.8611</v>
+        <v>-4.1523</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.8365</v>
+        <v>-1.937</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5908</v>
+        <v>-1.6205</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2457</v>
+        <v>-0.3165</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3907</v>
+        <v>-0.2557</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.5233</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2419</v>
+        <v>0.2676</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.4458</v>
+        <v>-1.6813</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-1.0973</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.4875</v>
+        <v>-0.5841</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R26" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7222</v>
+        <v>0.3463</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1383</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4161</v>
+        <v>-0.392</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.4799</v>
+        <v>-2.4937</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-12.9197</v>
+        <v>-12.284</v>
       </c>
       <c r="E27" t="n">
-        <v>3.7164</v>
+        <v>5.9312</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.6362</v>
+        <v>-18.2152</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.607799999999999</v>
+        <v>-5.8881</v>
       </c>
       <c r="H27" t="n">
-        <v>-9.709999999999999</v>
+        <v>-9.842199999999998</v>
       </c>
       <c r="I27" t="n">
-        <v>4.102399999999999</v>
+        <v>3.954299999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>7.1255</v>
+        <v>8.5578</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6541000000000001</v>
+        <v>1.6175</v>
       </c>
       <c r="L27" t="n">
-        <v>6.471399999999999</v>
+        <v>6.940299999999998</v>
       </c>
       <c r="M27" t="n">
-        <v>-12.7333</v>
+        <v>-14.4456</v>
       </c>
       <c r="N27" t="n">
-        <v>-10.3641</v>
+        <v>-11.4599</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.369</v>
+        <v>-2.9861</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.002000000000001</v>
+        <v>-6.815700000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>-15.0043</v>
+        <v>-14.6053</v>
       </c>
       <c r="R27" t="n">
-        <v>8.0023</v>
+        <v>7.7896</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6111999999999999</v>
+        <v>1.2366</v>
       </c>
       <c r="T27" t="n">
-        <v>3.858</v>
+        <v>3.9688</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.246900000000001</v>
+        <v>-2.7321</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.9211000000000007</v>
+        <v>-0.8168000000000002</v>
       </c>
       <c r="W27" t="n">
-        <v>7.7372</v>
+        <v>8.0101</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.658199999999999</v>
+        <v>-8.8269</v>
       </c>
     </row>
   </sheetData>
